--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>125757156</v>
       </c>
       <c r="B8" t="n">
-        <v>98213</v>
+        <v>98220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>125757156</v>
       </c>
       <c r="B8" t="n">
-        <v>98220</v>
+        <v>98223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>125757156</v>
       </c>
       <c r="B8" t="n">
-        <v>98223</v>
+        <v>98227</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>125757156</v>
       </c>
       <c r="B8" t="n">
-        <v>98227</v>
+        <v>98228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>125757156</v>
       </c>
       <c r="B8" t="n">
-        <v>98228</v>
+        <v>98230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>125757156</v>
       </c>
       <c r="B8" t="n">
-        <v>98230</v>
+        <v>98232</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>125757156</v>
       </c>
       <c r="B8" t="n">
-        <v>98232</v>
+        <v>98234</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>125757156</v>
       </c>
       <c r="B8" t="n">
-        <v>98234</v>
+        <v>98238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>125757156</v>
       </c>
       <c r="B8" t="n">
-        <v>98238</v>
+        <v>98241</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91835158</v>
+        <v>125757156</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>233</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Oakes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Staloberget, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>744093.0571503892</v>
+        <v>744464</v>
       </c>
       <c r="R2" t="n">
-        <v>7380923.014777577</v>
+        <v>7380752</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca 10 blommor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,33 +767,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91835156</v>
+        <v>91835155</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>744059.1959170685</v>
+        <v>744262</v>
       </c>
       <c r="R3" t="n">
-        <v>7380717.871583337</v>
+        <v>7381081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +854,9 @@
           <t>2020-06-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91835155</v>
+        <v>98309136</v>
       </c>
       <c r="B4" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>388</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>744262.217261272</v>
+        <v>744159</v>
       </c>
       <c r="R4" t="n">
-        <v>7381080.974431004</v>
+        <v>7380781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +973,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98308895</v>
+        <v>91835156</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>744095.6063277301</v>
+        <v>744059</v>
       </c>
       <c r="R5" t="n">
-        <v>7380926.052332547</v>
+        <v>7380718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1045,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1070,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98308906</v>
+        <v>91835158</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>744432.1604667814</v>
+        <v>744093</v>
       </c>
       <c r="R6" t="n">
-        <v>7380727.38233874</v>
+        <v>7380923</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,22 +1142,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1167,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98309136</v>
+        <v>98308895</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1185,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>744159.4687663454</v>
+        <v>744095</v>
       </c>
       <c r="R7" t="n">
-        <v>7380780.951896147</v>
+        <v>7380926</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1242,9 @@
           <t>2021-06-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,63 +1264,55 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125757156</v>
+        <v>98308906</v>
       </c>
       <c r="B8" t="n">
-        <v>98241</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>233</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Staloberget, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>744464</v>
+        <v>744432</v>
       </c>
       <c r="R8" t="n">
-        <v>7380752</v>
+        <v>7380727</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,17 +1336,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 10 blommor</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,34 +1350,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91835157</v>
+        <v>98309135</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,16 +1379,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1498,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743978.8790495918</v>
+        <v>744107</v>
       </c>
       <c r="R9" t="n">
-        <v>7380207.94865338</v>
+        <v>7380290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,22 +1433,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,10 +1458,107 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>91835157</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>743979</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7380208</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
           <t>Adam Helleberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91835156</v>
+        <v>135525457</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,34 +991,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Staloberget, Lu lm</t>
+          <t>Staloberget, Staloberget, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>744059</v>
+        <v>744510</v>
       </c>
       <c r="R5" t="n">
-        <v>7380718</v>
+        <v>7380689</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1065,19 +1065,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91835158</v>
+        <v>91835156</v>
       </c>
       <c r="B6" t="n">
         <v>80432</v>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>744093</v>
+        <v>744059</v>
       </c>
       <c r="R6" t="n">
-        <v>7380923</v>
+        <v>7380718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,7 +1174,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98308895</v>
+        <v>91835158</v>
       </c>
       <c r="B7" t="n">
         <v>80432</v>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>744095</v>
+        <v>744093</v>
       </c>
       <c r="R7" t="n">
-        <v>7380926</v>
+        <v>7380923</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1264,14 +1264,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98308906</v>
+        <v>98308895</v>
       </c>
       <c r="B8" t="n">
         <v>80432</v>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>744432</v>
+        <v>744095</v>
       </c>
       <c r="R8" t="n">
-        <v>7380727</v>
+        <v>7380926</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98309135</v>
+        <v>98308906</v>
       </c>
       <c r="B9" t="n">
-        <v>57874</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,21 +1379,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100001</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>744107</v>
+        <v>744432</v>
       </c>
       <c r="R9" t="n">
-        <v>7380290</v>
+        <v>7380727</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1458,17 +1458,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91835157</v>
+        <v>135525620</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>80488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,34 +1476,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Staloberget, Lu lm</t>
+          <t>Staloberget, Staloberget, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743979</v>
+        <v>744458</v>
       </c>
       <c r="R10" t="n">
-        <v>7380208</v>
+        <v>7380728</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1550,15 +1550,1664 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135525424</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>744526</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7380639</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135525581</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>744469</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7380739</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135525768</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>744475</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7380759</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135525340</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>744546</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7380674</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135525369</v>
+      </c>
+      <c r="B15" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>744531</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7380654</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135525319</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>744567</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7380672</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135525396</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>744524</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7380644</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135525599</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>744471</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7380740</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135525732</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>744468</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7380763</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135525789</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>744462</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7380761</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135525823</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>744450</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7380748</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135526164</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>744447</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7380747</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135526402</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>744512</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7380835</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135526225</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>744456</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7380744</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135526368</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>744487</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7380830</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>98309135</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57874</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>744107</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7380290</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-06-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-06-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>Sture Westerberg</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>91835157</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>743979</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7380208</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Adam Helleberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125757156</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835155</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98309136</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525457</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835156</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835158</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98308895</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98308906</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525620</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1656,6 +1706,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525424</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1753,6 +1808,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525581</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1850,6 +1910,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525768</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1947,6 +2012,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525340</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525369</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525319</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2238,6 +2318,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525396</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2335,6 +2420,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525599</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2432,6 +2522,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525732</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2529,6 +2624,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525789</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2626,6 +2726,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525823</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2723,6 +2828,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135526164</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2820,6 +2930,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135526402</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2917,6 +3032,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135526225</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3014,6 +3134,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135526368</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3111,6 +3236,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98309135</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3208,8 +3338,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835157</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>135525457</v>
       </c>
       <c r="B5" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135525620</v>
       </c>
       <c r="B10" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>135525424</v>
       </c>
       <c r="B11" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>135525581</v>
       </c>
       <c r="B12" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>135525768</v>
       </c>
       <c r="B13" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>135525340</v>
       </c>
       <c r="B14" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>135525369</v>
       </c>
       <c r="B15" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>135525319</v>
       </c>
       <c r="B16" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135525396</v>
       </c>
       <c r="B17" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>135525599</v>
       </c>
       <c r="B18" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>135525732</v>
       </c>
       <c r="B19" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>135525789</v>
       </c>
       <c r="B20" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135525823</v>
       </c>
       <c r="B21" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>135526164</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>135526402</v>
       </c>
       <c r="B23" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135526225</v>
       </c>
       <c r="B24" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>135526368</v>
       </c>
       <c r="B25" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>135525457</v>
       </c>
       <c r="B5" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135525620</v>
       </c>
       <c r="B10" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>135525424</v>
       </c>
       <c r="B11" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>135525581</v>
       </c>
       <c r="B12" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>135525768</v>
       </c>
       <c r="B13" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>135525340</v>
       </c>
       <c r="B14" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>135525369</v>
       </c>
       <c r="B15" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>135525319</v>
       </c>
       <c r="B16" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135525396</v>
       </c>
       <c r="B17" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>135525599</v>
       </c>
       <c r="B18" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>135525732</v>
       </c>
       <c r="B19" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>135525789</v>
       </c>
       <c r="B20" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135525823</v>
       </c>
       <c r="B21" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>135526164</v>
       </c>
       <c r="B22" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>135526402</v>
       </c>
       <c r="B23" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135526225</v>
       </c>
       <c r="B24" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>135526368</v>
       </c>
       <c r="B25" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91835156</v>
+        <v>135525457</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>93345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,34 +1011,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Staloberget, Lu lm</t>
+          <t>Staloberget, Staloberget, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>744059</v>
+        <v>744510</v>
       </c>
       <c r="R5" t="n">
-        <v>7380718</v>
+        <v>7380689</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,24 +1085,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91835156</t>
+          <t>https://artportalen.se/Sighting/135525457</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91835158</v>
+        <v>91835156</v>
       </c>
       <c r="B6" t="n">
         <v>80432</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>744093</v>
+        <v>744059</v>
       </c>
       <c r="R6" t="n">
-        <v>7380923</v>
+        <v>7380718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,13 +1198,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91835158</t>
+          <t>https://artportalen.se/Sighting/91835156</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98308895</v>
+        <v>91835158</v>
       </c>
       <c r="B7" t="n">
         <v>80432</v>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>744095</v>
+        <v>744093</v>
       </c>
       <c r="R7" t="n">
-        <v>7380926</v>
+        <v>7380923</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,19 +1294,19 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Adam Helleberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98308895</t>
+          <t>https://artportalen.se/Sighting/91835158</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98308906</v>
+        <v>98308895</v>
       </c>
       <c r="B8" t="n">
         <v>80432</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>744432</v>
+        <v>744095</v>
       </c>
       <c r="R8" t="n">
-        <v>7380727</v>
+        <v>7380926</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,16 +1402,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98308906</t>
+          <t>https://artportalen.se/Sighting/98308895</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98309135</v>
+        <v>98308906</v>
       </c>
       <c r="B9" t="n">
-        <v>57874</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100001</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>744107</v>
+        <v>744432</v>
       </c>
       <c r="R9" t="n">
-        <v>7380290</v>
+        <v>7380727</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,22 +1498,22 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98309135</t>
+          <t>https://artportalen.se/Sighting/98308906</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91835157</v>
+        <v>135525620</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>80556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,34 +1521,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Staloberget, Lu lm</t>
+          <t>Staloberget, Staloberget, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743979</v>
+        <v>744458</v>
       </c>
       <c r="R10" t="n">
-        <v>7380208</v>
+        <v>7380728</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,16 +1595,1750 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Adam Helleberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525620</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135525424</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>744526</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7380639</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525424</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135525581</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>744469</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7380739</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525581</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135525768</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>744475</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7380759</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525768</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135525340</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98295</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>744546</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7380674</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525340</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135525369</v>
+      </c>
+      <c r="B15" t="n">
+        <v>111242</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>744531</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7380654</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525369</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135525319</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>744567</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7380672</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525319</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135525396</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>744524</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7380644</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525396</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135525599</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>744471</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7380740</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525599</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135525732</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>744468</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7380763</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525732</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135525789</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>744462</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7380761</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525789</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135525823</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>744450</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7380748</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525823</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135526164</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>744447</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7380747</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135526164</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135526402</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>744512</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7380835</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135526402</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135526225</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>744456</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7380744</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135526225</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135526368</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Staloberget, Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>744487</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7380830</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135526368</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>98309135</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57874</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>744107</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7380290</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-06-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-06-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98309135</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>91835157</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Staloberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>743979</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7380208</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Adam Helleberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/91835157</t>
         </is>
@@ -1621,6 +3355,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>135525457</v>
       </c>
       <c r="B5" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>135525768</v>
       </c>
       <c r="B13" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>135525340</v>
       </c>
       <c r="B14" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>135525369</v>
       </c>
       <c r="B15" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>135525319</v>
       </c>
       <c r="B16" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135525396</v>
       </c>
       <c r="B17" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>135525599</v>
       </c>
       <c r="B18" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>135525732</v>
       </c>
       <c r="B19" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>135525789</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135525823</v>
       </c>
       <c r="B21" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>135526164</v>
       </c>
       <c r="B22" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>135526402</v>
       </c>
       <c r="B23" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135526225</v>
       </c>
       <c r="B24" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>135526368</v>
       </c>
       <c r="B25" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>135525457</v>
       </c>
       <c r="B5" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135525620</v>
       </c>
       <c r="B10" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>135525424</v>
       </c>
       <c r="B11" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>135525581</v>
       </c>
       <c r="B12" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>135525768</v>
       </c>
       <c r="B13" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>135525340</v>
       </c>
       <c r="B14" t="n">
-        <v>98297</v>
+        <v>98314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>135525369</v>
       </c>
       <c r="B15" t="n">
-        <v>111244</v>
+        <v>111267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>135525319</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135525396</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>135525599</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>135525732</v>
       </c>
       <c r="B19" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>135525789</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135525823</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>135526164</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>135526402</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135526225</v>
       </c>
       <c r="B24" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>135526368</v>
       </c>
       <c r="B25" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54960-2021 artfynd.xlsx
+++ b/artfynd/A 54960-2021 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>135525457</v>
       </c>
       <c r="B5" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>135525620</v>
       </c>
       <c r="B10" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>135525424</v>
       </c>
       <c r="B11" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>135525581</v>
       </c>
       <c r="B12" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>135525768</v>
       </c>
       <c r="B13" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>135525340</v>
       </c>
       <c r="B14" t="n">
-        <v>98314</v>
+        <v>98315</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>135525369</v>
       </c>
       <c r="B15" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>135525319</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135525396</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>135525599</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>135525732</v>
       </c>
       <c r="B19" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>135525789</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135525823</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>135526164</v>
       </c>
       <c r="B22" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>135526402</v>
       </c>
       <c r="B23" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135526225</v>
       </c>
       <c r="B24" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>135526368</v>
       </c>
       <c r="B25" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
